--- a/reports/Debug-purgatory-20260111/For The Day (Prior Year)_Revenue.xlsx
+++ b/reports/Debug-purgatory-20260111/For The Day (Prior Year)_Revenue.xlsx
@@ -97,10 +97,10 @@
     <t>account</t>
   </si>
   <si>
+    <t>T110</t>
+  </si>
+  <si>
     <t>T105</t>
-  </si>
-  <si>
-    <t>T110</t>
   </si>
   <si>
     <t>T100</t>
@@ -581,7 +581,7 @@
         <v>31</v>
       </c>
       <c r="D2" s="2">
-        <v>348.00</v>
+        <v>270.00</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -595,7 +595,7 @@
         <v>31</v>
       </c>
       <c r="D3" s="2">
-        <v>270.00</v>
+        <v>348.00</v>
       </c>
     </row>
     <row r="4" spans="1:4">
